--- a/out/08_ISMS/SNX-ISMS-REG-03 IS Risk Treatment Plan (Rev00 DRAFT).xlsx
+++ b/out/08_ISMS/SNX-ISMS-REG-03 IS Risk Treatment Plan (Rev00 DRAFT).xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rencana Penanganan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rencana Penanganan'!$A$4:$R$59</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Rencana Penanganan'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -167,7 +169,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -297,6 +299,33 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -736,8 +765,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="23">
-      <c r="A4" s="26" t="inlineStr">
+    <row r="3" s="23">
+      <c r="A3" s="44" t="n"/>
+      <c r="B3" s="44" t="n"/>
+      <c r="C3" s="44" t="n"/>
+      <c r="D3" s="44" t="n"/>
+      <c r="E3" s="44" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="23">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -747,9 +783,12 @@
           <t>SNX-ISMS-REG-03</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="23">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="44" t="n"/>
+      <c r="E4" s="44" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="23">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -759,9 +798,12 @@
           <t>Information Security Risk Treatment Plan</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="23">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="44" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="23">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -771,9 +813,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="23">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="23">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -783,9 +828,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="23">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="23">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -795,9 +843,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="23">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="23">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -807,9 +858,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="23">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="23">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -819,9 +873,12 @@
           <t>ISMS Coordinator</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="23">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="23">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -831,9 +888,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="23">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="23">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -843,9 +903,12 @@
           <t>Klausul 6.1</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="23">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="23">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -855,9 +918,12 @@
           <t>Klausul 6.1.3, 8.3</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="23">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="23">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -867,52 +933,75 @@
           <t>Berlaku sampai digantikan</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="23">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="23">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Rencana penanganan risiko keamanan informasi (klausul 6.1.3 dan 8.3), termasuk risiko residual dan penerimaan oleh pemilik risiko.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="23">
-      <c r="A17" s="28" t="inlineStr">
+          <t>Mencatat rencana penanganan risiko keamanan informasi (klausul 6.1.3 dan 8.3), termasuk risiko residual dan penerimaannya oleh pemilik risiko.</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+    </row>
+    <row r="16" s="23">
+      <c r="A16" s="44" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="23">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="23">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="23">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>Satu baris per tindakan penanganan; Ref risiko merujuk SNX-ISMS-REG-02.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="23">
-      <c r="A19" s="29" t="inlineStr">
+          <t>Isi satu baris untuk setiap tindakan penanganan. Kolom Ref risiko diisi ID risiko dari SNX-ISMS-REG-02.</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1" s="23">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>L dan I residual berisi usulan; ubah setelah tindakan selesai. Level otomatis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="23">
-      <c r="A20" s="29" t="inlineStr">
+          <t>Nilai L residual dan I residual masih berupa usulan. Perbarui nilainya setelah tindakan selesai; Level residual terisi otomatis.</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="23">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
@@ -922,9 +1011,12 @@
           <t>Risiko residual harus diterima pemilik risiko secara tertulis (kolom Diterima oleh dan Tgl penerimaan).</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="23.85" customHeight="1" s="23">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="23">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
@@ -934,85 +1026,122 @@
           <t>Kontrol Annex A yang dipilih di sini menjadi dasar kolom Berlaku pada SoA SNX-ISMS-SOA-01.</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="23.85" customHeight="1" s="23">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+    </row>
+    <row r="22" ht="43.5" customHeight="1" s="23">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>Usulan awal Divisi Operation dari riwayat operasi di knowledge base SINUX; wajib divalidasi ISMS Coordinator dan pemilik risiko.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="23">
-      <c r="A24" s="28" t="inlineStr">
+          <t>Baris usulan awal disusun Divisi Operation dari riwayat operasi di knowledge base SINUX. Baris tersebut wajib divalidasi ISMS Coordinator dan pemilik risiko.</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
+    </row>
+    <row r="23" s="23">
+      <c r="A23" s="44" t="n"/>
+      <c r="B23" s="44" t="n"/>
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="44" t="n"/>
+      <c r="E23" s="44" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="23">
+      <c r="A24" s="46" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="23">
-      <c r="A25" s="31" t="n"/>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B24" s="44" t="n"/>
+      <c r="C24" s="44" t="n"/>
+      <c r="D24" s="44" t="n"/>
+      <c r="E24" s="44" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="23">
+      <c r="A25" s="47" t="n"/>
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="23">
-      <c r="A26" s="32" t="n"/>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="23">
+      <c r="A26" s="48" t="n"/>
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Biru muda: usulan awal Divisi Operation, belum divalidasi</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="23">
-      <c r="A27" s="33" t="n"/>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="23">
+      <c r="A27" s="49" t="n"/>
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="23">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+    </row>
+    <row r="28" s="23">
+      <c r="A28" s="44" t="n"/>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="23">
+      <c r="A29" s="46" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="23">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="44" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="44" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="23">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B30" s="34" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C30" s="34" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
+      <c r="D30" s="38" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
+      <c r="E30" s="38" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="23.85" customHeight="1" s="23">
+    <row r="31" ht="30" customHeight="1" s="23">
       <c r="A31" s="27" t="inlineStr">
         <is>
           <t>00</t>
@@ -1046,76 +1175,91 @@
       <c r="D32" s="27" t="n"/>
       <c r="E32" s="27" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="23">
-      <c r="A34" s="28" t="inlineStr">
+    <row r="33" s="23">
+      <c r="A33" s="44" t="n"/>
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="44" t="n"/>
+      <c r="E33" s="44" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="23">
+      <c r="A34" s="46" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="23">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="B34" s="44" t="n"/>
+      <c r="C34" s="44" t="n"/>
+      <c r="D34" s="44" t="n"/>
+      <c r="E34" s="44" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="23">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="38" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="D35" s="38" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E35" s="44" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="23">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C36" s="35" t="n"/>
-      <c r="D36" s="35" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="44" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="23">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B37" s="27" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C37" s="35" t="n"/>
-      <c r="D37" s="35" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="44" t="n"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="23">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C38" s="35" t="n"/>
-      <c r="D38" s="35" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="44" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1159,100 +1303,104 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="22" min="1" max="3"/>
+    <col width="13" customWidth="1" style="23" min="2" max="2"/>
+    <col width="13" customWidth="1" style="23" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="23">
-      <c r="A1" s="37" t="inlineStr">
+    <row r="1" ht="16.5" customHeight="1" s="23">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Opsi</t>
         </is>
       </c>
-      <c r="B1" s="37" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="37" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Skala</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="23">
-      <c r="A2" s="29" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="23">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Mitigasi</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="51" t="inlineStr">
         <is>
           <t>Belum mulai</t>
         </is>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="51" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="23">
-      <c r="A3" s="29" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="23">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>Hindari</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>Berjalan</t>
         </is>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="51" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="23">
-      <c r="A4" s="29" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="23">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Selesai</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="51" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="23">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="23">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Terima</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Tertunda</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="51" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="23">
-      <c r="C6" s="29" t="n">
+      <c r="A6" s="52" t="n"/>
+      <c r="B6" s="52" t="n"/>
+      <c r="C6" s="51" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1266,6 +1414,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="22" min="1" max="2"/>
+    <col width="13" customWidth="1" style="23" min="2" max="2"/>
     <col width="32" customWidth="1" style="22" min="3" max="3"/>
     <col width="9" customWidth="1" style="22" min="4" max="4"/>
     <col width="10" customWidth="1" style="22" min="5" max="5"/>
@@ -1274,10 +1423,13 @@
     <col width="16" customWidth="1" style="22" min="8" max="8"/>
     <col width="14" customWidth="1" style="22" min="9" max="9"/>
     <col width="11" customWidth="1" style="22" min="10" max="11"/>
-    <col width="7" customWidth="1" style="22" min="12" max="14"/>
-    <col width="9" customWidth="1" style="22" min="15" max="15"/>
+    <col width="13" customWidth="1" style="23" min="11" max="11"/>
+    <col width="12" customWidth="1" style="22" min="12" max="14"/>
+    <col width="13" customWidth="1" style="23" min="13" max="13"/>
+    <col width="13" customWidth="1" style="23" min="14" max="14"/>
+    <col width="12" customWidth="1" style="22" min="15" max="15"/>
     <col width="16" customWidth="1" style="22" min="16" max="16"/>
-    <col width="11" customWidth="1" style="22" min="17" max="17"/>
+    <col width="15" customWidth="1" style="22" min="17" max="17"/>
     <col width="20" customWidth="1" style="22" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -1291,11 +1443,11 @@
     <row r="2" ht="15" customHeight="1" s="23">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Target tanggal dan residual adalah usulan; ditetapkan bersama pemilik risiko. Status vault (RTP-001, RTP-010): menunggu konfirmasi Ops.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" s="23">
+          <t>Target selesai dan nilai residual masih usulan, ditetapkan bersama pemilik risiko. Status vault pada RTP-001 dan RTP-010 menunggu konfirmasi Divisi Operation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="43.5" customHeight="1" s="23">
       <c r="A4" s="38" t="inlineStr">
         <is>
           <t>ID RTP</t>
@@ -1387,7 +1539,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="23.85" customHeight="1" s="23">
+    <row r="5" ht="57" customHeight="1" s="23">
       <c r="A5" s="39" t="inlineStr">
         <is>
           <t>RTP-001</t>
@@ -1455,7 +1607,7 @@
       <c r="Q5" s="40" t="n"/>
       <c r="R5" s="39" t="n"/>
     </row>
-    <row r="6" ht="35.05" customHeight="1" s="23">
+    <row r="6" ht="57" customHeight="1" s="23">
       <c r="A6" s="39" t="inlineStr">
         <is>
           <t>RTP-002</t>
@@ -1523,7 +1675,7 @@
       <c r="Q6" s="40" t="n"/>
       <c r="R6" s="39" t="n"/>
     </row>
-    <row r="7" ht="23.85" customHeight="1" s="23">
+    <row r="7" ht="43.5" customHeight="1" s="23">
       <c r="A7" s="39" t="inlineStr">
         <is>
           <t>RTP-003</t>
@@ -1591,7 +1743,7 @@
       <c r="Q7" s="40" t="n"/>
       <c r="R7" s="39" t="n"/>
     </row>
-    <row r="8" ht="35.05" customHeight="1" s="23">
+    <row r="8" ht="57" customHeight="1" s="23">
       <c r="A8" s="39" t="inlineStr">
         <is>
           <t>RTP-004</t>
@@ -1659,7 +1811,7 @@
       <c r="Q8" s="40" t="n"/>
       <c r="R8" s="39" t="n"/>
     </row>
-    <row r="9" ht="35.05" customHeight="1" s="23">
+    <row r="9" ht="43.5" customHeight="1" s="23">
       <c r="A9" s="39" t="inlineStr">
         <is>
           <t>RTP-005</t>
@@ -1727,7 +1879,7 @@
       <c r="Q9" s="40" t="n"/>
       <c r="R9" s="39" t="n"/>
     </row>
-    <row r="10" ht="35.05" customHeight="1" s="23">
+    <row r="10" ht="43.5" customHeight="1" s="23">
       <c r="A10" s="39" t="inlineStr">
         <is>
           <t>RTP-006</t>
@@ -1795,7 +1947,7 @@
       <c r="Q10" s="40" t="n"/>
       <c r="R10" s="39" t="n"/>
     </row>
-    <row r="11" ht="23.85" customHeight="1" s="23">
+    <row r="11" ht="43.5" customHeight="1" s="23">
       <c r="A11" s="39" t="inlineStr">
         <is>
           <t>RTP-007</t>
@@ -1863,7 +2015,7 @@
       <c r="Q11" s="40" t="n"/>
       <c r="R11" s="39" t="n"/>
     </row>
-    <row r="12" ht="35.05" customHeight="1" s="23">
+    <row r="12" ht="57" customHeight="1" s="23">
       <c r="A12" s="39" t="inlineStr">
         <is>
           <t>RTP-008</t>
@@ -1931,7 +2083,7 @@
       <c r="Q12" s="40" t="n"/>
       <c r="R12" s="39" t="n"/>
     </row>
-    <row r="13" ht="35.05" customHeight="1" s="23">
+    <row r="13" ht="43.5" customHeight="1" s="23">
       <c r="A13" s="39" t="inlineStr">
         <is>
           <t>RTP-009</t>
@@ -1999,7 +2151,7 @@
       <c r="Q13" s="40" t="n"/>
       <c r="R13" s="39" t="n"/>
     </row>
-    <row r="14" ht="23.85" customHeight="1" s="23">
+    <row r="14" ht="43.5" customHeight="1" s="23">
       <c r="A14" s="39" t="inlineStr">
         <is>
           <t>RTP-010</t>
@@ -2067,7 +2219,7 @@
       <c r="Q14" s="40" t="n"/>
       <c r="R14" s="39" t="n"/>
     </row>
-    <row r="15" ht="35.05" customHeight="1" s="23">
+    <row r="15" ht="57" customHeight="1" s="23">
       <c r="A15" s="39" t="inlineStr">
         <is>
           <t>RTP-011</t>
@@ -2135,7 +2287,7 @@
       <c r="Q15" s="40" t="n"/>
       <c r="R15" s="39" t="n"/>
     </row>
-    <row r="16" ht="23.85" customHeight="1" s="23">
+    <row r="16" ht="43.5" customHeight="1" s="23">
       <c r="A16" s="39" t="inlineStr">
         <is>
           <t>RTP-012</t>
@@ -2203,7 +2355,7 @@
       <c r="Q16" s="40" t="n"/>
       <c r="R16" s="39" t="n"/>
     </row>
-    <row r="17" ht="23.85" customHeight="1" s="23">
+    <row r="17" ht="43.5" customHeight="1" s="23">
       <c r="A17" s="39" t="inlineStr">
         <is>
           <t>RTP-013</t>
@@ -2271,7 +2423,7 @@
       <c r="Q17" s="40" t="n"/>
       <c r="R17" s="39" t="n"/>
     </row>
-    <row r="18" ht="23.85" customHeight="1" s="23">
+    <row r="18" ht="43.5" customHeight="1" s="23">
       <c r="A18" s="39" t="inlineStr">
         <is>
           <t>RTP-014</t>
@@ -2339,7 +2491,7 @@
       <c r="Q18" s="40" t="n"/>
       <c r="R18" s="39" t="n"/>
     </row>
-    <row r="19" ht="23.85" customHeight="1" s="23">
+    <row r="19" ht="43.5" customHeight="1" s="23">
       <c r="A19" s="39" t="inlineStr">
         <is>
           <t>RTP-015</t>
@@ -3508,6 +3660,6 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>